--- a/validation/arch35/results/a5_950_20260714/atk_accuracy/atk_accuracy_reports.xlsx
+++ b/validation/arch35/results/a5_950_20260714/atk_accuracy/atk_accuracy_reports.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>{"id":0,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"bd3f7d76-f1e7-4d22-bad7-457ffec3075c","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":0,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"51e2f2c6-c2b6-4fd7-b278-165b2c6863dd","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>{"id":1,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"891cf9f5-2adc-405e-8cda-a3cc02e1d72b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":1,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f0c35648-fc91-47f3-a67f-7504f3f65edb","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>{"id":2,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b9385e00-8e6a-43e1-a119-8a8179bc9d24","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":2,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2b90b583-4299-4a91-91f3-3d99cce1ff67","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>{"id":3,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ddce28a0-f430-492b-8122-c3ef920ae11b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":3,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"16212258-38fa-48b6-b8e3-861c8960be24","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>{"id":4,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"463a387e-db9b-48f3-98c3-cb18c54dff8c","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":4,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a41e7175-d557-4ed0-b49e-bd2f7083d687","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>{"id":5,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"79d286da-9e98-40e3-8e38-c3b89370d6de","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":5,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"66517386-8ede-499d-aeb0-c12602f4c757","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>{"id":6,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6d27c0b1-55b1-4ca7-ae45-aba974f28106","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":6,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"91f5ca29-b7d9-4bb0-8b37-a32548599a95","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>{"id":7,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c728fc3c-cacb-4301-a377-b4f69f7609ac","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":7,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2c28d6e9-eb19-4b9d-9035-78dab164592b","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>{"id":8,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"7ac5fb73-f373-4663-af78-3e104484128f","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":8,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8262845d-27be-4ef6-9606-861932760989","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>{"id":9,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"29f6c1ed-1d83-4d26-bf75-5bbee64c2f30","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":9,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8ebd99f9-9723-4c3e-8055-c5efbf9e5f02","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>{"id":10,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"17ca0498-85b2-4ae5-9d62-989484e295d3","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":10,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b1025479-00ad-4786-b581-da1d9d7945ed","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>{"id":11,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6fe713bb-6694-4d19-a863-a248f3d87ca0","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":11,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d0ffbd5b-ff31-4c62-a71e-a8abfc7dc85a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>{"id":12,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"af18a600-9e9b-404c-8aae-7daf1f3c6ba4","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":12,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6ed7d654-aed1-42ac-8cbe-8baa48228841","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>{"id":13,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"7ff2b094-c4d3-4e02-91b0-7bf774e23ead","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":13,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e291be4c-1273-4b5e-b55a-3c1067c8257a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>{"id":14,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b722f617-02bd-470c-b524-0aa71c13bf9e","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":14,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8bc3bf5f-fcc5-47ac-898f-1c7dbe1cda8c","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>{"id":15,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"77e61bd7-d426-4a7c-b8bb-4c401317fa7e","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":15,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"cdee1bc8-6468-4c5a-a01d-d849f5aad8c6","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>{"id":16,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8616a6a3-c0b2-417c-9a94-80e5ad3fa046","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":16,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a3b08f83-c914-49fd-a341-5bd66614bbe5","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>{"id":17,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"087e8086-3bf1-48e3-ae22-6cdd85185f85","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":17,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9063fc5e-0323-4d6f-96fc-3e58618a9b56","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>{"id":18,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9aa2e0ab-6929-435c-8a07-a237a5c05a0e","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":18,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2ad67952-25aa-40bb-9c3a-f9e60a5937db","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>{"id":19,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5b56a0e0-d33a-4415-bfb1-769bb8dbd868","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":19,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8380e725-95fa-4f82-882d-662a5e33b3e4","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>{"id":20,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"14d40334-212e-466d-a224-de457470a8bf","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":20,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"842b61bd-29fb-44b8-a8bd-675874a288e8","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>{"id":21,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"49434929-e7d5-403c-b682-4b1883eeb27a","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":21,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9f6c7757-4b98-49c7-8d4d-b076823f0a7f","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>{"id":22,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9eba4dd8-499d-4487-b4b3-9ee165e3a32b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":22,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d8494a0c-af89-4544-8d56-e58c56387078","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>{"id":23,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e2e6886b-2630-4120-bbc5-cfb4d9e404b6","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":23,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"7c90c839-e817-491a-bce5-e90b555549f0","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>{"id":24,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0f451924-2001-4f48-beb9-e6c037b5fa36","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":24,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"87f2edb3-0323-4f9d-83d7-529d3a04a01a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>{"id":25,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"15fa5458-2e75-4cb5-a670-85214a200baa","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":25,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"45050f7e-3194-450b-992f-3aa48b9a2b0e","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>{"id":26,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d59895d6-44bb-4a94-b9b9-656f76ba1844","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":26,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"cdf66e19-424c-40a7-93fa-757caf7992f3","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>{"id":27,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"623a9c88-52b7-4713-80ae-418f3e731f38","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":27,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"edd99eab-8769-400d-85ef-0c70789dc96e","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>{"id":28,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ed181a08-50b6-4f41-8d2e-d416ad7ecb22","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":28,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e76f4e60-a934-4b69-94d9-08197a5ba773","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>{"id":29,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6b8bedef-0f44-4104-814d-ac65b2b66d15","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":29,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9b4a90fb-c573-4c06-a835-89c814dc3a6b","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>{"id":30,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9a342370-30de-4c4e-8220-ee33e73c9668","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":30,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2c7a0534-1b66-4ea4-b0b2-e84bc3466cee","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>{"id":31,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d503be7b-c172-4077-b780-37eb2401a514","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":31,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e7d51c99-4111-43e2-8cb4-a02933a0a892","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>{"id":32,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4a02263f-b25a-4010-adb8-e643e9847d3e","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":32,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5c12776e-1724-48a4-b7bb-8ae7c7e07102","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>{"id":33,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"07626ac5-255a-4ac9-a4b7-0915eefd5ae3","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":33,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"460bb5ec-9e0e-4344-929f-63631ce51526","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>{"id":34,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b95dd25d-d10a-4e97-8f28-9a7be06f5df9","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":34,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"330ac157-b32a-4ca9-a5cf-b466bce91b78","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>{"id":35,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"69867eb2-1c50-4a82-a7be-62d40cd94ac9","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":35,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,4],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[3,4],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6a3384cc-0290-4903-9cd8-79969dc21df7","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>{"id":36,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"acbfca80-49e1-4785-ba71-d3989017ccf2","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":36,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ea2e80b5-c90a-4ef0-8f03-fa0d0d5024c0","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>{"id":37,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1f434c0e-d6e9-40c7-8998-8a6ac1098ba4","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":37,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1444c070-8860-41b8-8d14-1363a1a298de","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>{"id":38,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1571f6ca-37b2-4c67-a07d-736c707765b3","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":38,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c7a76273-a46b-41a6-993a-95a7cde9e69f","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>{"id":39,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"71c7460d-5f26-4128-8724-f10349a64f57","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":39,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"bc7524bb-1ae8-4dcf-a0a4-fd049acfcbee","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>{"id":40,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"fe29c248-2e09-42e1-a777-c08a260be2a2","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":40,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"138a0046-ca49-4034-ad5e-5f0f536192b4","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>{"id":41,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a9d296f8-122c-428b-a343-0611a79df518","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":41,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"02f74202-b2cf-4d51-bdae-d2f355970e65","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>{"id":42,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"dc6ab349-59ef-4d66-8bde-23a3500ddea8","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":42,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a33f5e43-d09a-49c7-8cd1-a876e692e36d","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>{"id":43,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5556b45f-ccbf-4eba-9712-85b63ac05f90","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":43,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f391db7b-37b6-477a-8e5b-e5c45bfa2336","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>{"id":44,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f1b8cbac-6b16-4da5-8ca1-5693298def96","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":44,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f2e0aafd-17cc-41eb-8007-3429b3d1579d","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>{"id":45,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"427c5c93-3ed8-4380-b9aa-66df6192bbd3","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":45,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"84d5aeb0-8708-4b1e-bbbb-6a8dd3282c41","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>{"id":46,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6d255f34-3906-463f-8828-549aeabcf233","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":46,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6288aef9-2466-4a3d-9458-440c62284a7f","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>{"id":47,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6caacd61-8226-4e06-9edc-206f15543c26","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":47,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[8,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f6ab96bd-e851-4b21-9844-41bc170822d2","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>{"id":48,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e4af441d-b9e2-42a2-be25-d3f36e01db60","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":48,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8a22a569-a5ca-48c7-8e10-5eb414182eeb","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>{"id":49,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3406a096-95d2-4724-a862-3387059ada0c","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":49,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f891e711-107a-41f5-83fd-510b69107191","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>{"id":50,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"01091082-04b7-42aa-9080-b8252d040b96","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":50,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"49ae88ef-7ff7-47fb-b020-b8abc79d6f32","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>{"id":51,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b57c8b90-7724-4fa4-b637-738c2d89c821","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":51,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e2883b79-f7b0-4200-a67e-114a12deed32","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>{"id":52,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4d0ceeff-1491-427d-a1da-635073e8f50b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":52,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6d368ed9-b475-4c3d-9337-ee9f7988d8f5","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>{"id":53,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f8b21286-7f76-4d32-b9fb-6a6e78c2712e","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":53,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0da736d4-c802-45d1-8eca-b78741c7dfd1","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>{"id":54,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"53555b2a-4e0f-4a64-ba21-e03eeee5262f","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":54,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ad756b6a-7bd4-4c28-b9ec-942fa1bcb096","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>{"id":55,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"585aa70b-89b4-4009-8277-097686bc3da6","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":55,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a32bbcc2-5986-4d9c-9b31-3bedbd550799","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>{"id":56,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b6e4c1b7-5214-4cdd-b9f4-430fb2ba912e","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":56,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d40fb83d-5e35-4cab-9301-5d281e9741c9","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>{"id":57,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"fa99aed1-286e-403d-b4df-625d88abee21","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":57,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"245c452e-a168-4fa5-a9fc-2e01ae7b55b3","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>{"id":58,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a6aa3dcc-3fea-45a2-a14f-d46b7876e553","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":58,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"66952bad-d4e2-47c3-a6df-e725e23f21b0","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>{"id":59,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3a40f035-149e-4c1c-900a-6665d44bfdc5","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":59,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"94c7dada-b188-4630-8af9-a32a11d4c397","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>{"id":60,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"885c767b-bf6e-419c-94ed-1a79ac937e03","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":60,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"18de809b-7802-41d7-9316-c0c872bcb786","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>{"id":61,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"051d7bc5-0213-4500-9c02-36c8dfc38078","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":61,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"78d67d90-4301-48b4-bbd6-6bfc889cb6c7","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>{"id":62,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0af6b3f9-9968-4f2f-81e0-ff3190b95e99","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":62,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c844fd5f-7b4b-4954-ab2a-1b0fcf59700a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>{"id":63,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"89d7e11e-b7b8-4efb-9844-12a1beeb4789","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":63,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9a71f2a3-d51e-4646-805e-b7aed9663687","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>{"id":64,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"efb7b269-b78e-4698-a5a9-1b267516f344","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":64,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8c4be60c-68fb-4e36-887b-e77cba37e71f","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>{"id":65,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"811ed64a-ce41-451c-9b9d-7fcf942ead50","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":65,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4d148afc-2641-4a47-8a8a-e10be095d304","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>{"id":66,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a276ddd9-bf1e-4eaf-8da7-ecbc6b3b0266","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":66,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b341a05d-977a-440b-8546-454d2c6a4041","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>{"id":67,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"007892ce-629f-4fac-8e6f-cd4fca82823b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":67,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c0924009-b45a-4e22-b9a0-1ae03f3e1d7a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>{"id":68,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"690ab7bd-0121-4207-82a3-610c8e4e9825","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":68,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"688b6d94-6b6c-47cb-9018-474f6a1b2ec5","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>{"id":69,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"602a6013-5c16-4da6-80f4-c2ee0a35cb8f","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":69,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9b4ba7cf-4d22-420c-948d-cf3419242c3b","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>{"id":70,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a145b74f-203d-4de8-bc33-49b1c08cab46","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":70,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"68930830-0aa5-40ad-9a3e-a25892ba298d","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>{"id":71,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d58236ce-46c3-45c6-964d-28d50b33ea09","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":71,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"250ded2f-0260-4c8c-9d75-0b906dda3321","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>{"id":72,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a9e7037e-9757-49f1-a98c-b62e977423a7","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":72,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"41ec6e68-7c40-4d75-a3fe-b4f78e584ffe","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>{"id":73,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c427d175-4fe3-4ea7-abf3-5d8f89c174ac","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":73,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0ee07454-a4a1-4967-a58a-16455e08d0e8","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>{"id":74,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3a8ffc51-c260-425e-b5fc-a4b4f722fce2","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":74,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"764a509b-e35b-418d-ae33-11f0f8dfd212","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>{"id":75,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8be5d703-cb9f-4f60-b26e-13b5def2d844","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":75,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5f7b2d69-d2b0-4569-a64c-ffdd506c9148","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>{"id":76,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5dcd1281-3372-4e20-9ba3-d403d584292d","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":76,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"580a9864-5720-404b-a5b1-1a2e84570a23","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>{"id":77,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ec86bb9d-dfbf-4988-9ee7-8b9424b21101","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":77,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"323a4c94-4fa3-4b1e-a49e-8268a95a327b","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>{"id":78,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1a123aa6-5ced-4c64-924d-d0e96242e2a7","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":78,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a8fb6984-2cf6-4176-a569-692d38613e27","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>{"id":79,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f3b44757-b2a0-4767-b67c-7807108c93cf","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":79,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"81b616bc-ff9d-4f64-8800-d98335b3b4cd","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>{"id":80,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"516d1b3e-8e1c-4631-bf45-c32305c8fa4b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":80,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e47f0fb5-2096-40da-99e1-684fc1c3c6ac","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>{"id":81,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"7d0d9fb7-fe60-42ba-b0be-ecf1dc7beeb3","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":81,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"72a62133-cd97-4dc6-acc1-caea998d0366","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>{"id":82,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"40baed60-d5c4-4b19-8edf-cf703812c09c","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":82,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d46266d5-bc7a-447a-a17e-2785c4106cb6","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>{"id":83,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"76ede743-fd21-4839-afd8-1c3f616dff1d","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":83,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[128,128],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[128],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4016efc8-2b9a-4a2b-8aaa-b32fc572f232","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>{"id":84,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"61ed68e6-e20a-4b3f-b436-c6e0f1cd943d","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":84,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b1eab90d-ed70-4fd1-b112-1b3c4a0cf610","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>{"id":85,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1da004f4-11da-4d44-9fcf-b4628ea5d04a","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":85,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"bec0165b-34e3-4301-a07a-6286a3466583","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>{"id":86,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ab70ca48-8b8f-4467-b3bd-d4e16f3ca8a3","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":86,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"59da61eb-be29-42ba-93c9-6b2a7ddd6f9d","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>{"id":87,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c2b49c1d-404e-41f7-ade2-b2058289fe92","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":87,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"57a96e7c-82d5-4052-accf-39b1da9e71ef","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>{"id":88,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b673b2b7-e9f9-43b0-808c-1096eaa07b3f","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":88,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d3820642-c069-4e94-a5d6-cdea1bf2a8ff","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>{"id":89,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"213e7221-a1c5-44f8-a511-7ba4ee81668d","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":89,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c4410752-cc19-454c-a0b8-6d179241d9d6","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>{"id":90,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2c976cc7-84ae-46d0-bc27-eaa211976a9c","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":90,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f5531967-2c66-43df-ae91-79dea0363eae","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>{"id":91,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"322d3383-6154-44f8-b382-a6e55d5fd0f8","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":91,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4d4e17ab-472c-4574-bcbd-d811bb9619a3","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>{"id":92,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"772bc0ba-35fd-4025-a2dc-44849b1224c2","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":92,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"7f41e89a-ef14-4b7f-8e44-aad03109ce28","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>{"id":93,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ef579826-931b-49e5-ad41-9f9fdcf8f38b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":93,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"03d48b20-b687-4683-93f3-e02c823d8142","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>{"id":94,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"751b3e64-1093-4045-9e6d-f59e5ca69a28","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":94,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5fd905e1-94e2-47a0-9aa5-0e653b6bf509","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>{"id":95,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ce1a0816-451d-4f28-abc1-ace442d803bd","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":95,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,8192],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[8192],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b3c14480-fdc5-4dc4-9a3a-b077d855586d","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>{"id":96,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"982bca20-86eb-4d11-8e88-0ca39a306058","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":96,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"628dbaa3-a354-4cb8-8a59-add656d80084","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>{"id":97,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"42eb1902-0124-4a86-a622-654a62f3e81b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":97,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d1a2c15d-dd02-48f6-a09f-bfbb52938425","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>{"id":98,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b462f7ec-aa10-4b4c-99ab-e6f89cb3af86","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":98,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6e9b0843-83a5-4ea0-a331-6e43580b35b4","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>{"id":99,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5c01d746-0a80-4367-bf10-4dbe49811617","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":99,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6922c7f9-9c64-4e33-9414-98762ee7c942","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>{"id":100,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9b737bf5-afb2-4467-a180-414747e4d64a","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":100,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e0416075-1c52-4644-9f32-4f08067ae1b3","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>{"id":101,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"de931260-12e7-43cf-8bd1-cb564617f265","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":101,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a16812da-f231-4e49-8d3b-d8cc86ba7677","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5519,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>{"id":102,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b4f60803-dfb1-466c-a473-4096f203ccb0","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":102,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"cbd469a5-4666-4ad9-a37a-997ad54ac097","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>{"id":103,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"bf989ee3-3f44-4fe9-920b-9125424c40fa","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":103,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"12041d0b-48d5-4e75-8a01-0c1c8eec25a5","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>{"id":104,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"aae8ca11-4e02-41ac-a505-38b97c0e8d92","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":104,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b4bd17d0-c73c-4ce2-8496-87117d51ad95","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>{"id":105,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1347c5e7-9f8a-48c6-8710-67684c687d49","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":105,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c5250bdf-3e75-43ee-b792-b7f5ea46f0e8","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>{"id":106,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f1e383e3-2512-472c-99aa-c3601fde9f03","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":106,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2076a4bb-a1d3-4486-99b7-72e9411895ef","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>{"id":107,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2797e427-31a3-48a4-b01e-7a183059a370","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":107,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[7,21,16,9],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16,9],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8d05fde7-0858-4709-8a0a-b41b790b7b79","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>{"id":108,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"cac0aed8-efce-42ef-a278-d61e48f202b8","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":108,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9973b57c-c492-4e6d-bb7f-2ecb9e6bce15","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>{"id":109,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"af09e6fd-681a-47d7-8da7-17d04e231125","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":109,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"18c13780-6729-4c18-a1fc-4819a59b832d","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>{"id":110,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0e572a25-dd1e-4b22-97da-0508130f757d","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":110,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"cc4cd8e9-7cc0-4638-a698-06ba55c8f179","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>{"id":111,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0c158580-e9e7-47f2-9335-0fc1bc3c3cd4","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":111,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"54d50e6d-7e4a-4ba7-b73f-4f7cb6492f43","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>{"id":112,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d043632b-303e-4d0c-9293-61109a21c7f5","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":112,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d098bb80-0562-455b-bbaf-0fda6600bd2c","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>{"id":113,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1fcb3dcb-e9b8-4afa-af4e-3381c4ccc5e9","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":113,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a83dda2f-95fe-4a7f-8716-91234bf3a04d","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>{"id":114,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d063c477-5c49-4867-a874-b477a0ab0187","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":114,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e6cfb95e-8003-42a7-8a2d-10374658934c","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>{"id":115,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"fc0ca112-00eb-4d69-89d3-155d4b183da6","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":115,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1beba9dc-430d-4686-8925-6f7b43687c02","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>{"id":116,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c82940ec-a68f-48d2-9cf6-5cc33b3c753f","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":116,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1ba2db8d-ecfa-4b02-b6ec-0e0151d93b48","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>{"id":117,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d3fd8d7f-6a16-42d6-a138-22e223f2f55a","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":117,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"03cc547c-90fc-460c-959d-961f263b3e4a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>{"id":118,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3e23b49c-4bdc-40ec-a9a7-cedd37d9c9c1","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":118,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6ecde110-c571-4743-bd6e-fc87dbbb917f","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>{"id":119,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a328f44e-e838-47b2-9aaa-99f4d2c6992c","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":119,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,20,7,16,9,1,1],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[20,7,16,9,1,1],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1f3004a0-1f56-4742-bb11-9b0a72f9dd36","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>{"id":120,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9f6f2952-c6c7-4a86-b760-f4544e1a2de8","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":120,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f1d0c172-6c50-4ea2-a160-e6a48ce5077e","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>{"id":121,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"902e4d8d-ccf2-4baf-9f6d-d8defa263715","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":121,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d292e6c2-d628-4559-95a4-be91eeab3265","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>{"id":122,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"308a9242-2374-49b7-9346-3085f027fda5","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":122,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8bfa2876-3afb-4128-a257-67a8b914d143","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>{"id":123,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b500c43d-8802-4bfa-95f2-53baf9dbf14a","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":123,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b4d6cb91-fc6e-4cad-80a4-aad291c142d2","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>{"id":124,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a2c18af6-7b1a-4f65-b63f-d1c1507304f1","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":124,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"eec25069-542d-4758-9ddd-2de25ddcd809","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>{"id":125,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9cbefbcb-ef53-4ed6-a092-868f4ca18141","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":125,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"356cba76-37ec-45ff-bc9b-3e8aff573ae0","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>{"id":126,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"7103e439-735c-4551-91da-7328e455f729","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":126,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c26b1a3b-dba1-4de0-b718-196c132bb342","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>{"id":127,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"7a1c2f87-906b-4ba5-a8f4-cae7e6d49e2d","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":127,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1042b1a8-45aa-4ce0-93b3-4a72ecffec53","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>{"id":128,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"99bc91ee-2d3f-4fbe-a7f7-d5ed4320edc7","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":128,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"7408678b-953c-4ee5-9a96-b57205af6c90","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>{"id":129,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f5df4854-9061-4139-8d16-ed477d9e1dd4","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":129,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a48325b1-c642-4501-a4cc-435d1b7a1766","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>{"id":130,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0d037788-150f-4f96-b8d4-1876efa7d2cd","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":130,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ed2be30e-84f1-4ff2-8190-5839a4875e4a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>{"id":131,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3f78414c-f193-41b8-b444-f3e146fe9204","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":131,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,1,9,9,1,256],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1,9,9,1,256],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2c293c15-ffe8-449d-87e9-539cc5d7fd48","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>{"id":132,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6763f0f2-f56a-49d4-9578-c5229c3e687c","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":132,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"cf4a54d3-781c-49ae-a0b4-875e9e17a476","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>{"id":133,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"556fab4a-3aef-4c74-8a36-896396a49906","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":133,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a608edb8-e610-42eb-99c3-952077d67b5f","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>{"id":134,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8c433ba8-0cfe-41ba-9323-29555c73b8e5","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":134,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"484e5b36-1ca2-4040-9608-e937ee1890dd","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>{"id":135,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"770bf18e-fa20-4919-a36f-3a1807a07238","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":135,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ccda6aec-9274-49f7-894c-a53d4190aa44","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>{"id":136,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2297ed1f-0775-452f-aaf1-308bb76d7110","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":136,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5f6d5ad8-eef5-4a9c-a4be-0a58361df387","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>{"id":137,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1bb1fe7e-2561-4b44-a74a-79b9fed0a6f8","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":137,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2b7d83a5-57d8-4898-a299-0b83e737cc64","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>{"id":138,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8f818007-892b-4d0a-8d65-d0a861b74a4b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":138,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4232e2ff-e765-48f4-8f18-219c8bf55473","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>{"id":139,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"af72e9b9-dffb-4691-a5dd-2f30afc449c5","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":139,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b5711d94-9b46-4669-9711-a262ee618275","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>{"id":140,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"20c8447f-0641-4e9d-9db6-1e650ebb38d4","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":140,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"baf3001a-4463-4adf-8270-094b38732823","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>{"id":141,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"cdf3a0fd-4161-4a3b-8531-b8c47fae2ea9","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":141,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"579e71a4-4b77-4add-9e62-dc415bf1b969","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>{"id":142,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a432eba5-86bf-4202-bcb8-77eb6125f541","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":142,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"7a6066dc-1593-4329-8ca0-d91e7fcf65a6","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>{"id":143,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"bba1c6df-5438-4630-960b-7c7dab1f3035","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":143,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,3,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"25717de8-ce35-43b4-8671-f1098daae555","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>{"id":144,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f176f87a-0434-4fba-86b3-11954884c11e","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":144,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3584b15b-ed31-4b61-85da-0e402b849f47","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>{"id":145,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a8038883-66cd-4d71-8d19-02e1d77675df","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":145,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"469d66ea-04a5-4d26-8c3f-82fc79601c02","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>{"id":146,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"eca67785-938a-4915-94ba-ff593c56fb91","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":146,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"342b6bfd-c92a-4387-ad2b-3d846b59d711","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>{"id":147,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4290516a-3718-43da-a9db-e13c5cea1e20","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":147,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"386219a3-6848-436e-bb65-dadebf4b3b04","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>{"id":148,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c08cfa64-9ebf-49db-babc-c2de3167b68b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":148,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a3ec03a3-39f6-47c4-9da1-843e9d14de6f","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>{"id":149,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"aab07f55-afeb-4aff-b7f9-de681b03b118","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":149,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1341bde2-80a8-40fd-b392-028d83be9ddc","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>{"id":150,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ff41df5f-25f6-4d0b-a43a-278bfac3edb9","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":150,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"982e6505-67bd-40fb-bc2c-ea12b2f3c8d2","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>{"id":151,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ccc9291c-8b84-45d9-993c-2b83363bbf5f","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":151,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"25961514-9d73-4a11-8dd5-2fcea20df99e","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>{"id":152,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"347bf352-0e68-447e-a830-fb1ea6fa475b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":152,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f497f73f-07bb-42de-a8f9-01f8f35cb950","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>{"id":153,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3212b808-f44f-4dd3-8033-b31f124dcafb","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":153,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0f133637-432f-4f15-b6df-22e5751bf909","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>{"id":154,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c417b84e-8fd9-4913-bbf9-f00ee6d92bf8","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":154,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b5f2cb79-ea7a-4a59-8e2f-d492e69274e1","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>{"id":155,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f5abb9ba-9da6-49fc-b744-5a6a8cc18501","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":155,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[2,16384],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[16384],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b1a6abb5-6aca-431a-953a-cb7d493f4a22","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>{"id":156,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"77a3196c-54fa-476b-953a-e261d5abe01b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":156,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"780f6ec5-4b5c-41b0-91e8-6cbf8febbdfd","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>{"id":157,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9a71926e-e1cc-4fb2-86ac-38f6ff146ff5","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":157,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d20a7bf2-4180-411b-a119-81acfc04db70","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>{"id":158,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"be9c764e-9aaf-4d02-953a-5c7d5142efa6","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":158,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2478e997-d05e-473f-913e-e8f588b8467e","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>{"id":159,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1d68a7a0-76e9-4a0b-b981-fc4cc5204481","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":159,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6fdcdb13-082b-4c5a-b201-f2a488449ece","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>{"id":160,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0a5b2909-6840-4032-bef9-cf94b94aabd2","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":160,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e7187183-10f7-4ef3-995f-298aaa723e3d","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>{"id":161,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"711284bc-5ef8-4b4f-908a-1b0a80745110","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":161,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"04e8c329-fa0e-477e-8904-f716709bf8d3","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>{"id":162,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"15f2b45f-5c52-4e1e-a173-f7049cae502e","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":162,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"23e6eee3-ea87-4647-9ce5-6601a08bd85c","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>{"id":163,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"fb624371-6255-4566-b1da-f84b052524ec","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":163,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2033f6bb-b2aa-4f63-92e6-0135d3964543","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>{"id":164,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"16010c9f-9dea-4e94-bfed-366250dd78f6","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":164,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"fe867098-89ba-4d53-a9fe-4f841ed3ac46","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>{"id":165,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"07560a79-a075-4b24-8e78-7992d78f8407","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":165,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"abc5a785-f4b8-439f-ad10-b2922ea26bfb","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>{"id":166,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a609f119-dd73-41e0-ac95-6f9a64f01ce1","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":166,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0f304b29-e4a8-4179-b702-bd0beac46ccb","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>{"id":167,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9ec497aa-eb09-44da-8b08-56f13daf7859","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":167,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[1,32768],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[32768],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0f5ead32-e012-40f4-883c-0585875f6891","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>{"id":168,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0d9d2d01-4429-435c-bfcc-8bfe0073e58c","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":168,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c146efe8-6c7c-494d-9a1e-1c572d6e19fa","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>{"id":169,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e22531c9-3347-4920-8aed-274742103aca","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":169,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9109bb6a-6375-4b40-9b87-330e33edd9ed","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>{"id":170,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a33b2f10-a00e-466f-938a-c3b52781e86d","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":170,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"47c41921-827d-4058-b0ab-6c342014ef61","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>{"id":171,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0f96db5b-731e-43a0-b6e4-4bb65a173aa0","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":171,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"86b12809-6954-4dbe-9139-5e3117267638","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>{"id":172,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c8c76178-7b06-4659-9a39-6d03fa817f76","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":172,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5eb7739e-e646-4c8f-98fd-c856c358960a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>{"id":173,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9c48431c-d72b-45ae-8fa9-2df89ebf3f31","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":173,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"58289f18-ad96-4dd4-bfbb-3741d441ff96","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>{"id":174,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c1309d9e-2c39-4e22-bd01-06def3668d2c","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":174,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c2d75fd8-be9d-4427-b8b3-8065c28b8d76","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>{"id":175,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d167e621-f593-4675-a9dc-5e2d80e02868","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":175,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ba3db0cb-82b7-430e-afb9-decbfc0c9e5d","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>{"id":176,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"96b67359-343d-4520-be25-67a2829aab8c","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":176,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"61693721-d039-40d1-8295-8737128f9e2a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>{"id":177,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f822aa74-ef38-495c-83e4-5112f649d4c5","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":177,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3bc65db8-5ba7-4096-9207-8436b15e9a66","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>{"id":178,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"284acc35-976f-4040-af57-76d2efb56d46","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":178,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3a97e6b0-7961-4ad5-8966-7aae1ace3016","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>{"id":179,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b6c877ce-fec3-441e-bd3d-01ee9a64f49b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":179,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,1024],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[1024],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6ff46364-6add-4324-b762-f3252d147d12","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>{"id":180,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"734d4f1a-f250-4ee4-b2e7-d842c5d168ee","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":180,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6fa5708d-88a3-4a54-8a9d-ca98edf79120","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>{"id":181,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"55e8ebc4-222f-4f6a-bd66-4984d747c1d3","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":181,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"053fddd6-f61b-4575-95fc-660134744376","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>{"id":182,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"631ebe1d-bc9c-40a0-8dc9-1ea79b7eca05","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":182,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"bec58fd1-0a5b-4a38-9052-02378218b86c","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>{"id":183,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d0faf094-8cee-44cf-8cb1-10863fa6293f","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":183,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4906b10e-9ded-4034-bfd5-2dfc59c360bb","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>{"id":184,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ff6a1411-22b5-464a-8333-260a8efe7cd5","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":184,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"79a47a2a-53f6-44c6-8ca2-2f6d307deee8","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>{"id":185,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"454d8a12-9870-4aa5-870e-ab29d6e34e20","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":185,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9144f38e-291e-4716-964c-fbfcdb914d0b","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>{"id":186,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"66f279c7-2fd9-4a9b-b315-de62d2f92914","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":186,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b5fcfa7c-e990-40fe-b473-f52ca04d884e","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>{"id":187,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f51b130e-8901-460d-87e3-1f98c2422d90","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":187,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"20bdad83-cfb5-4bab-8d9f-12516d6e679b","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>{"id":188,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2a20f1e8-4009-47c5-b408-534a5642c3c2","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":188,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c25edb72-851a-4d44-bffc-7a1bc2e361c3","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>{"id":189,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b4043bc7-f5b9-4650-98bf-2d2daa17e188","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":189,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"bf407ac3-1a77-4602-9c13-5e56a7ae9530","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>{"id":190,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2e4b884a-0a64-42e3-97fb-42256716cdd8","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":190,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"91761ae0-fb15-43ba-b1ec-a7181bc24150","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>{"id":191,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f38aa18c-02da-47ab-b610-48f477afce39","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":191,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,2048],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[2048],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ce7a1e68-246d-40bd-8005-5f1ec186efff","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>{"id":192,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c5197ec5-8625-43b1-9793-136e4c4e56ea","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":192,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1bbc26c0-8ee5-4020-a149-aef1d013e5e4","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>{"id":193,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"373a3eba-75da-4491-b7f8-3a79307fe6ff","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":193,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"329902d3-aefa-45e8-a5c1-946ec2aac0ec","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>{"id":194,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b0962745-d485-4370-952b-48025a2a9c6f","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":194,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c27eeef9-43d1-4670-b76a-ac8cebe50c61","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>{"id":195,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b13fa65e-f4fe-4cce-a4a5-909a5d93dbc9","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":195,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5eb4febe-b1ed-4a8e-8201-83764d6bb092","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>{"id":196,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"464e6029-90a2-412b-a7b1-5096632751ca","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":196,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ead51bcf-65d8-4fbd-9f39-9e9e93cb477f","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>{"id":197,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"57cf1e68-5a10-44f3-b51c-e648ec855ada","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":197,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"62f8a905-f706-4dc1-9446-1d5d644da283","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>{"id":198,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b6ca8edb-ad97-4725-9bc8-34ff540ab307","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":198,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b40805fd-96b9-40b1-9b1d-709c52d83006","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>{"id":199,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"75cadb2b-1feb-4af3-9443-d3a745176a23","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":199,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"37956d79-aa1f-43f5-b745-e8201c3a101a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10321,7 +10321,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>{"id":200,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a11f71b9-5783-47d8-a0fe-b743f5225081","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":200,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"25769517-32b1-4483-b2dd-2d1e249bdecc","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>{"id":201,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4545f5e3-9f8e-4d12-9b92-783b4d491fa1","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":201,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8b6e3e57-82cc-4173-a930-8fcb7b9d92f9","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>{"id":202,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5bcdccf2-9cb2-4edd-8f6d-d3acc0eab96e","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":202,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"981f386e-e9b2-4db5-b0ae-7a69ef405833","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>{"id":203,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e21f0129-6ab4-4040-956e-ee67946663de","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":203,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"612af664-fb60-4a15-b275-cd371423f3f8","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>{"id":204,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"fa603e8c-a4cc-456e-b7bd-027e865d33a6","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":204,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"25ca482d-7a90-4614-95ca-e8e7dd0a1230","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>{"id":205,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8b259319-1ffc-40b0-8172-4750124f454f","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":205,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"51977193-8f46-474b-80bf-d9f169e03810","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>{"id":206,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e6c95198-1b22-4b0d-805d-81c080a2c045","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":206,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"bb4103d5-1715-4b7a-84b2-f91115dd64fc","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>{"id":207,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"112fb00c-a2fa-4886-a306-ccef68304380","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":207,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"8a6802aa-07a1-4956-b0a5-d4994d25ac7a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10713,7 +10713,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>{"id":208,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3697cf7c-7087-482e-94ea-e3dd6e18e780","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":208,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"169daf7b-6085-4098-ad23-b530244dcef3","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>{"id":209,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"32aab93e-4f8a-4d6d-a21b-03ad8c63fe30","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":209,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2f535f04-befb-4982-91a3-5d1fbc09251e","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10811,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>{"id":210,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1f83f299-4035-4d33-99f3-158c2008f788","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":210,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"da76e300-4fcf-4459-8b5e-80809254fccf","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>{"id":211,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2ea7d8ea-9b4b-4301-9307-1762e755c264","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":211,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"605d858c-7708-406d-b07a-5248dfc448ce","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>{"id":212,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4903e0f0-45f9-4296-a84f-bb7f4be39daf","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":212,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f4798234-e624-42f8-afb8-46581c571b13","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>{"id":213,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4e2435eb-6411-4c04-af15-253a13c4bd8c","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":213,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"12819ac8-71bb-43ed-b1cd-41e1c7bd32a3","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>{"id":214,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"121d3097-9f67-4844-ae1b-192fed287eba","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":214,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"6ee610f9-5fef-48db-b9e8-5c3223f472bb","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>{"id":215,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e1a3eb76-5135-4260-a52c-fbd81370fd7d","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":215,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[31,7168],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[7168],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"90bba6b7-b06b-4044-a491-7c0637c88d3a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>{"id":216,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"7d4b2543-653f-4042-830e-f8011735c7ae","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":216,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a19271d4-094f-4f28-b457-cfc51dfd0037","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>{"id":217,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"417ca1a1-8951-46b6-a080-ec2221d87e2b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":217,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4dbf2891-574f-4225-b8b1-7500bc9fa6b4","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11203,7 +11203,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>{"id":218,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"20f8110b-1f15-4ca4-a73a-c2fce3045073","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":218,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"2f5d90cf-8b4b-4010-a692-55cd44f4b0ce","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>{"id":219,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"10c4c7ec-3548-48f5-9263-d513e0e310de","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":219,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c9acaf58-9202-4794-9832-750b70cf714a","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>{"id":220,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"9ca98bef-56f9-424e-a540-9075a7c7b25d","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":220,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4ea01cd0-c4a8-4718-b5be-7a2e6dcaa598","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11350,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>{"id":221,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4c15f47b-6595-4068-b19f-f4cfc6100212","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":221,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1547cfb9-282e-4987-9f1b-39400232b256","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>{"id":222,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"654a4752-1721-406a-92c7-2341d5648c59","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":222,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"40961bd0-bfd0-4544-83c3-704a9077b690","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>{"id":223,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"75ac202b-0c49-4870-b6e6-c7d83778b099","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":223,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"662bff4b-ed0f-4769-9448-b6299f297b10","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>{"id":224,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"7a44cdf4-0fc5-4b2b-93c0-f0bcb05058c5","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":224,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e624c9fc-7712-40bd-8d6a-88cce5c19e65","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>{"id":225,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"bf6e4002-240c-42de-8991-9a1ea400710d","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":225,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"ac963ddb-9371-45b8-9d10-a71c67814ee1","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>{"id":226,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"0202a9af-26a5-4df4-a06d-f017ba93d381","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":226,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"23b77354-aebb-406c-bfa4-650744f139f7","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>{"id":227,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"db5476a3-d9d2-4110-9a1d-ff3d3690ca26","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":227,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[64,4096],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[4096],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b9cc6517-2aa2-4925-91b5-be32a22071c3","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>{"id":228,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"365271df-aff2-40a1-a84f-4d836811c923","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":228,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"99591cf6-871e-4e6b-bae3-c3bafc27bdb4","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>{"id":229,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"c01f978d-e441-4478-9576-5ed3f1a2090d","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":229,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"1850fe66-c765-489d-902b-b32d95f8d476","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>{"id":230,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"978fb866-8970-40de-b58f-9184164bde95","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":230,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"886757fb-bec4-443a-9855-c80aa8f6574c","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>{"id":231,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"239f1a0e-3bf6-4bbd-b357-7adbdcf57137","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":231,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[1],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3fd1de59-eded-49af-8995-ed498eb372cb","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11889,7 +11889,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>{"id":232,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"e076c239-557e-49b2-8533-91d87f759780","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":232,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"884821e9-f99e-4908-98a2-111735f8ceb5","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>{"id":233,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3edac7a6-326c-4783-8de6-2a253c5d547a","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":233,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f9276356-ff4b-4568-877e-d46bd47482c6","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>{"id":234,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"5862cc82-b385-4fe9-81ee-e39b26c2956b","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":234,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"a96e1b80-9763-4a32-ab89-bc3fb7a6aa61","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>{"id":235,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"f9b0728d-0df3-4b7e-acc7-ec024931c785","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":235,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"bf16","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"bf16","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[2],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d88dadff-bb82-4f5f-9b6f-cbe1429a7ab6","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -12085,7 +12085,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>{"id":236,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"acff5252-40ea-46d4-bced-444576bc12af","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":236,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"3bff0b25-d428-486e-a4c8-f8aeed19edc9","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>{"id":237,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"11f5abb4-e2d4-4f1f-bcc4-2c8215959f48","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":237,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-1,1],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"b078cdb0-6a34-4902-ac73-d129667fd892","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>{"id":238,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"08db7464-8a2e-4eed-8df2-0470889c6b51","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":238,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[true],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"4195ef87-fc44-400a-8f1d-597f9644ea01","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
@@ -12232,7 +12232,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>{"id":239,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"45ee26ec-8d38-4f91-bb95-04f6f15fc365","downloaded":false,"is_boundary":false}</t>
+          <t>{"id":239,"name":"GammaAddRmsNorm","aclnn_name":"GammaAddRmsNorm","version":null,"expected_error_msg":null,"api":"pytorch","api_type":"aclnn_gamma_add_rms_norm","aclnn_api_type":"sample_aclnn_api","backward":false,"standard":{"acc":"default","perf":"not_key"},"outputs":null,"inputs":[{"name":"x1","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"x2","type":"tensor","required":true,"dtype":"fp32","shape":[512,5120],"range_values":[-3,3],"backward":true,"align_32B":null,"outlier_values":null},{"name":"gamma","type":"tensor","required":true,"dtype":"fp32","shape":[5120],"range_values":[-0.5,0.5],"backward":true,"align_32B":null,"outlier_values":null},{"name":"epsilon","type":"attr","required":true,"dtype":"double","shape":null,"range_values":[1e-6],"backward":false,"align_32B":null,"outlier_values":null},{"name":"addGammaOffset","type":"attr","required":true,"dtype":"bool","shape":null,"range_values":[false],"backward":false,"align_32B":null,"outlier_values":null},{"name":"kernelType","type":"attr","required":true,"dtype":"int8_t","shape":null,"range_values":[3],"backward":false,"align_32B":null,"outlier_values":null}],"method_inputs":null,"tensor_input":null,"save_name":"atk_aclnnGammaAddRmsNorm_full_compat","uuid":"d9bb8195-1e9c-424a-a06e-4dc1324d838b","downloaded":false,"is_boundary":false}</t>
         </is>
       </c>
     </row>
